--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_6_объем_рынка_Similarweb_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_6_объем_рынка_Similarweb_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-89518d\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9752330F-07DB-47BD-88F0-B68511B652BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2149EEA9-D29F-4331-BAA5-56F1C521D9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -428,9 +428,6 @@
     <t>Вносите только сопоставимый период</t>
   </si>
   <si>
-    <t>Например, последние 3 месяца для всех сайтов</t>
-  </si>
-  <si>
     <t>Разделяйте весь трафик и релевантный трафик</t>
   </si>
   <si>
@@ -497,9 +494,6 @@
     <t>Display</t>
   </si>
   <si>
-    <t>example-agency.by</t>
-  </si>
-  <si>
     <t>прямой</t>
   </si>
   <si>
@@ -941,12 +935,6 @@
     <t>Комментарий / снимок экрана</t>
   </si>
   <si>
-    <t>Traffic &amp; Engagement</t>
-  </si>
-  <si>
-    <t>Демонстрационная строка</t>
-  </si>
-  <si>
     <t>EUR/год</t>
   </si>
   <si>
@@ -1131,6 +1119,18 @@
   </si>
   <si>
     <t>Не подтверждают платежеспособный спрос</t>
+  </si>
+  <si>
+    <t>Website performance</t>
+  </si>
+  <si>
+    <t>Visits, 3 months (06-08.2026)</t>
+  </si>
+  <si>
+    <t>Снимок Similarweb Pro 03.10.2026, файл similarweb_снимок_2026-10-03.csv</t>
+  </si>
+  <si>
+    <t>Последние 3 месяца (06-08.2026) для всех сайтов</t>
   </si>
 </sst>
 </file>
@@ -1282,13 +1282,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2081,16 +2081,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
       <c r="I1" s="21"/>
       <c r="J1" s="21"/>
       <c r="K1" s="21"/>
@@ -2345,16 +2345,16 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="11" customHeight="1">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:26" ht="27">
       <c r="A14" s="2" t="s">
@@ -2470,16 +2470,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
       <c r="I1" s="21"/>
       <c r="J1" s="21"/>
       <c r="K1" s="21"/>
@@ -2518,7 +2518,7 @@
         <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C4" t="s">
         <v>99</v>
@@ -2532,7 +2532,7 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
         <v>99</v>
@@ -2546,7 +2546,7 @@
         <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
         <v>99</v>
@@ -2659,16 +2659,16 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="11" customHeight="1">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" t="s">
@@ -2700,7 +2700,7 @@
         <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2708,10 +2708,10 @@
         <v>85</v>
       </c>
       <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
         <v>129</v>
-      </c>
-      <c r="C19" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2719,10 +2719,10 @@
         <v>89</v>
       </c>
       <c r="B20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" t="s">
         <v>131</v>
-      </c>
-      <c r="C20" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2761,27 +2761,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
       <c r="T1" s="21"/>
       <c r="U1" s="21"/>
       <c r="V1" s="21"/>
@@ -2792,58 +2792,58 @@
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>97</v>
@@ -2851,16 +2851,16 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E4" s="4">
         <v>154111</v>
@@ -2884,7 +2884,7 @@
       <c r="K4" s="10">
         <v>3.14</v>
       </c>
-      <c r="L4" s="24">
+      <c r="L4" s="22">
         <v>9.6064814814814819E-4</v>
       </c>
       <c r="M4" s="8">
@@ -2906,21 +2906,21 @@
         <v>3.3E-3</v>
       </c>
       <c r="S4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E5" s="4">
         <v>35325</v>
@@ -2946,7 +2946,7 @@
       <c r="K5" s="10">
         <v>1.84</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="22">
         <v>3.4722222222222224E-4</v>
       </c>
       <c r="M5" s="8">
@@ -2968,21 +2968,21 @@
         <v>2.7099999999999999E-2</v>
       </c>
       <c r="S5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E6" s="4">
         <v>241737</v>
@@ -3008,7 +3008,7 @@
       <c r="K6" s="10">
         <v>1.95</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="22">
         <v>4.2824074074074075E-4</v>
       </c>
       <c r="M6" s="8">
@@ -3030,21 +3030,21 @@
         <v>1.37E-2</v>
       </c>
       <c r="S6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E7" s="4">
         <v>202178</v>
@@ -3070,7 +3070,7 @@
       <c r="K7" s="10">
         <v>2.34</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="22">
         <v>3.3564814814814812E-4</v>
       </c>
       <c r="M7" s="8">
@@ -3092,21 +3092,21 @@
         <v>1.67E-2</v>
       </c>
       <c r="S7" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E8" s="4">
         <v>14688</v>
@@ -3132,7 +3132,7 @@
       <c r="K8" s="10">
         <v>1.72</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="22">
         <v>3.0092592592592595E-4</v>
       </c>
       <c r="M8" s="8">
@@ -3154,21 +3154,21 @@
         <v>9.2200000000000004E-2</v>
       </c>
       <c r="S8" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B9" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E9" s="4">
         <v>17824</v>
@@ -3194,7 +3194,7 @@
       <c r="K9" s="10">
         <v>2.0299999999999998</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="22">
         <v>3.5879629629629629E-4</v>
       </c>
       <c r="M9" s="8">
@@ -3216,21 +3216,21 @@
         <v>3.2199999999999999E-2</v>
       </c>
       <c r="S9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B10" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C10" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E10" s="4">
         <v>292214</v>
@@ -3256,7 +3256,7 @@
       <c r="K10" s="10">
         <v>3.09</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="22">
         <v>6.3657407407407413E-4</v>
       </c>
       <c r="M10" s="8">
@@ -3278,21 +3278,21 @@
         <v>7.000000000000001E-4</v>
       </c>
       <c r="S10" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B11" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C11" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E11" s="4">
         <v>116617</v>
@@ -3318,7 +3318,7 @@
       <c r="K11" s="10">
         <v>1.81</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="22">
         <v>3.2407407407407406E-4</v>
       </c>
       <c r="M11" s="8">
@@ -3340,21 +3340,21 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="S11" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B12" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C12" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E12" s="4">
         <v>222359</v>
@@ -3380,7 +3380,7 @@
       <c r="K12" s="10">
         <v>3.86</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="22">
         <v>2.3032407407407407E-3</v>
       </c>
       <c r="M12" s="8">
@@ -3402,21 +3402,21 @@
         <v>3.1099999999999999E-2</v>
       </c>
       <c r="S12" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B13" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C13" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E13" s="4">
         <v>701540</v>
@@ -3442,7 +3442,7 @@
       <c r="K13" s="10">
         <v>3.24</v>
       </c>
-      <c r="L13" s="24">
+      <c r="L13" s="22">
         <v>1.2037037037037038E-3</v>
       </c>
       <c r="M13" s="8">
@@ -3464,21 +3464,21 @@
         <v>3.3E-3</v>
       </c>
       <c r="S13" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B14" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C14" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E14" s="4">
         <v>1935</v>
@@ -3504,7 +3504,7 @@
       <c r="K14" s="10">
         <v>2.0499999999999998</v>
       </c>
-      <c r="L14" s="24">
+      <c r="L14" s="22">
         <v>6.3657407407407413E-4</v>
       </c>
       <c r="M14" s="8">
@@ -3526,21 +3526,21 @@
         <v>4.0300000000000002E-2</v>
       </c>
       <c r="S14" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E15" s="4">
         <v>5522</v>
@@ -3566,7 +3566,7 @@
       <c r="K15" s="10">
         <v>1.85</v>
       </c>
-      <c r="L15" s="24">
+      <c r="L15" s="22">
         <v>3.9351851851851852E-4</v>
       </c>
       <c r="M15" s="8">
@@ -3588,7 +3588,7 @@
         <v>3.0099999999999998E-2</v>
       </c>
       <c r="S15" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -3799,7 +3799,7 @@
     </row>
     <row r="25" spans="1:19" ht="13.9">
       <c r="A25" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -3954,16 +3954,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
       <c r="I1" s="21"/>
       <c r="J1" s="21"/>
       <c r="K1" s="21"/>
@@ -3985,33 +3985,33 @@
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" s="8">
         <f>'02_Конкуренты_SW'!M25</f>
@@ -4026,13 +4026,13 @@
         <v>814787.66483127279</v>
       </c>
       <c r="E4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" t="s">
         <v>165</v>
-      </c>
-      <c r="F4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G4" t="s">
-        <v>167</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" ref="H4:H9" si="1">IF(B4&gt;=0.3,"высокий",IF(B4&gt;=0.15,"средний","низкий"))</f>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B5" s="8">
         <f>'02_Конкуренты_SW'!N25</f>
@@ -4056,13 +4056,13 @@
         <v>639878.13451156358</v>
       </c>
       <c r="E5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" t="s">
         <v>168</v>
-      </c>
-      <c r="F5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G5" t="s">
-        <v>170</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="1"/>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" s="8">
         <f>'02_Конкуренты_SW'!O25</f>
@@ -4086,13 +4086,13 @@
         <v>131278.44499090911</v>
       </c>
       <c r="E6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" t="s">
         <v>171</v>
-      </c>
-      <c r="F6" t="s">
-        <v>172</v>
-      </c>
-      <c r="G6" t="s">
-        <v>173</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="1"/>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="8">
         <f>'02_Конкуренты_SW'!P25</f>
@@ -4116,13 +4116,13 @@
         <v>86264.603735563622</v>
       </c>
       <c r="E7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" t="s">
         <v>174</v>
-      </c>
-      <c r="F7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G7" t="s">
-        <v>176</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="1"/>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="8">
         <f>'02_Конкуренты_SW'!Q25</f>
@@ -4146,13 +4146,13 @@
         <v>83748.691117309092</v>
       </c>
       <c r="E8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" t="s">
         <v>177</v>
-      </c>
-      <c r="F8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" t="s">
-        <v>179</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="1"/>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B9" s="8">
         <f>'02_Конкуренты_SW'!R25</f>
@@ -4176,13 +4176,13 @@
         <v>44570.379012000005</v>
       </c>
       <c r="E9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" t="s">
         <v>180</v>
-      </c>
-      <c r="F9" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" t="s">
-        <v>182</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" si="1"/>
@@ -4255,16 +4255,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
       <c r="I1" s="21"/>
       <c r="J1" s="21"/>
       <c r="K1" s="21"/>
@@ -4286,25 +4286,25 @@
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>97</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B4" s="8">
         <v>0.1673</v>
@@ -4326,22 +4326,22 @@
         <v>318406.74925919995</v>
       </c>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G4" t="str">
         <f>IF(B4&gt;=0.35,"высокий",IF(B4&gt;=0.15,"средний","низкий"))</f>
         <v>средний</v>
       </c>
       <c r="H4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B5" s="8">
         <v>1.7299999999999999E-2</v>
@@ -4355,22 +4355,22 @@
         <v>32925.503659199996</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G5" t="str">
         <f>IF(B5&gt;=0.35,"высокий",IF(B5&gt;=0.15,"средний","низкий"))</f>
         <v>низкий</v>
       </c>
       <c r="H5" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B6" s="8">
         <v>2.5399999999999999E-2</v>
@@ -4384,22 +4384,22 @@
         <v>48341.490921599994</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G6" t="str">
         <f>IF(B6&gt;=0.35,"высокий",IF(B6&gt;=0.15,"средний","низкий"))</f>
         <v>низкий</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B7" s="8">
         <v>0.79</v>
@@ -4413,17 +4413,17 @@
         <v>1503534.5601599999</v>
       </c>
       <c r="E7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G7" t="str">
         <f>IF(B7&gt;=0.35,"высокий",IF(B7&gt;=0.15,"средний","низкий"))</f>
         <v>высокий</v>
       </c>
       <c r="H7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -4493,18 +4493,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
       <c r="K1" s="21"/>
       <c r="L1" s="21"/>
       <c r="M1" s="21"/>
@@ -4524,31 +4524,31 @@
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>97</v>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C4" s="8">
         <v>0.109</v>
@@ -4569,7 +4569,7 @@
         <v>17287.475427999998</v>
       </c>
       <c r="E4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F4" s="10">
         <v>1</v>
@@ -4579,21 +4579,21 @@
         <v>17287.475427999998</v>
       </c>
       <c r="H4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C5" s="8">
         <v>0.36599999999999999</v>
@@ -4603,7 +4603,7 @@
         <v>58047.853271999993</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F5" s="10">
         <v>0.6</v>
@@ -4613,21 +4613,21 @@
         <v>34828.711963199996</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C6" s="8">
         <v>0.45300000000000001</v>
@@ -4637,7 +4637,7 @@
         <v>71846.113475999999</v>
       </c>
       <c r="E6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F6" s="10">
         <v>0.25</v>
@@ -4647,21 +4647,21 @@
         <v>17961.528369</v>
       </c>
       <c r="H6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B7" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C7" s="8">
         <v>7.1999999999999995E-2</v>
@@ -4671,7 +4671,7 @@
         <v>11419.249823999999</v>
       </c>
       <c r="E7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F7" s="10">
         <v>0.1</v>
@@ -4681,13 +4681,13 @@
         <v>1141.9249823999999</v>
       </c>
       <c r="H7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -4803,18 +4803,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
       <c r="K1" s="21"/>
       <c r="L1" s="21"/>
       <c r="M1" s="21"/>
@@ -4833,54 +4833,54 @@
       <c r="Z1" s="21"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
+      <c r="A3" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:26" ht="27.75">
       <c r="A4" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B5" s="5">
         <v>0.7</v>
@@ -4916,7 +4916,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B6" s="5">
         <v>0.55000000000000004</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B7" s="5">
         <v>0.4</v>
@@ -4987,42 +4987,42 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="11" customHeight="1">
-      <c r="A10" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
+      <c r="A10" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" spans="1:26" ht="27.75">
       <c r="A11" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B12" s="12">
         <f>J5</f>
@@ -5036,15 +5036,15 @@
         <v>241.72365906727399</v>
       </c>
       <c r="E12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B13" s="12">
         <f>J6</f>
@@ -5058,15 +5058,15 @@
         <v>5741.0421230782786</v>
       </c>
       <c r="E13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B14" s="12">
         <f>J7</f>
@@ -5080,29 +5080,29 @@
         <v>87419.119229896605</v>
       </c>
       <c r="E14" t="s">
+        <v>223</v>
+      </c>
+      <c r="F14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="11" customHeight="1">
+      <c r="A17" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="F14" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="11" customHeight="1">
-      <c r="A17" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
     </row>
     <row r="18" spans="1:10" ht="108">
       <c r="A18" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -5116,22 +5116,22 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -5168,21 +5168,21 @@
     </row>
     <row r="21" spans="1:10" ht="27">
       <c r="A21" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B21" s="13">
         <f>J5</f>
         <v>48344.731813454797</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D21" s="13">
         <f>J6</f>
         <v>382736.14153855189</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F21" s="13">
         <f>J7</f>
@@ -5195,7 +5195,7 @@
     </row>
     <row r="22" spans="1:10" ht="94.5">
       <c r="A22" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B22" s="2" t="str">
         <f>"При заданных допущениях годовой объем цифрового рынка оценивается в диапазоне от "&amp;TEXT(J5,"# ##0")&amp;" до "&amp;TEXT(J7,"# ##0")&amp;" EUR, а достижимая выручка нового бизнеса — от "&amp;TEXT(D12,"# ##0")&amp;" до "&amp;TEXT(D14,"# ##0")&amp;" EUR в год."</f>
@@ -5241,20 +5241,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
       <c r="M1" s="21"/>
       <c r="N1" s="21"/>
       <c r="O1" s="21"/>
@@ -5271,52 +5271,52 @@
       <c r="Z1" s="21"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-    </row>
-    <row r="4" spans="1:26" ht="27.75">
+      <c r="A3" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+    </row>
+    <row r="4" spans="1:26" ht="40.5">
       <c r="A4" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B4" s="15" t="str">
         <f>'01_Параметры'!B4</f>
         <v>Онлайн-проверка Excel-моделей и финансовых таблиц (TableMind)</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D4" s="15" t="str">
         <f>'01_Параметры'!B5</f>
         <v>Англоязычные страны и ЕС-27</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F4" s="15">
         <f>'01_Параметры'!B8</f>
         <v>12</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H4" s="16">
         <f>'01_Параметры'!B9</f>
         <v>87230.380599999989</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J4" s="16">
         <f>'01_Параметры'!B12</f>
@@ -5325,35 +5325,35 @@
     </row>
     <row r="5" spans="1:26" ht="27.75">
       <c r="A5" s="14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B5" s="18">
         <f>'06_Воронка_сценарии'!J5</f>
         <v>48344.731813454797</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D5" s="18">
         <f>'06_Воронка_сценарии'!J6</f>
         <v>382736.14153855189</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F5" s="18">
         <f>'06_Воронка_сценарии'!J7</f>
         <v>2185477.9807474152</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H5" s="18">
         <f>'06_Воронка_сценарии'!D13</f>
         <v>5741.0421230782786</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J5" s="15" t="str">
         <f>INDEX('03_Каналы'!A4:A9,MATCH(MAX('03_Каналы'!B4:B9),'03_Каналы'!B4:B9,0))</f>
@@ -5362,28 +5362,28 @@
     </row>
     <row r="6" spans="1:26" ht="27.75">
       <c r="A6" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B6" s="15" t="str">
         <f>INDEX('02_Конкуренты_SW'!B4:B23,MATCH(MAX('02_Конкуренты_SW'!G4:G23),'02_Конкуренты_SW'!G4:G23,0))</f>
         <v>Datarails</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D6" s="20">
         <f>MAX('02_Конкуренты_SW'!I4:I23)</f>
         <v>0.26281225350975945</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F6" s="15" t="str">
         <f>INDEX('05_Запросы'!A4:A10,MATCH(MAX('05_Запросы'!G4:G10),'05_Запросы'!G4:G10,0))</f>
         <v>проблемные запросы (ошибки в формулах)</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H6" s="16">
         <f>MAX('05_Запросы'!G4:G10)</f>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="7" spans="1:26" ht="94.5">
       <c r="A7" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B7" s="15" t="str">
         <f>'06_Воронка_сценарии'!B22</f>
@@ -5411,18 +5411,18 @@
     </row>
     <row r="10" spans="1:26" ht="27.75">
       <c r="A10" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="12">
         <f>'06_Воронка_сценарии'!J5</f>
@@ -5435,7 +5435,7 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B12" s="12">
         <f>'06_Воронка_сценарии'!J6</f>
@@ -5448,7 +5448,7 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B13" s="12">
         <f>'06_Воронка_сценарии'!J7</f>
@@ -5461,18 +5461,18 @@
     </row>
     <row r="16" spans="1:26" ht="13.9">
       <c r="A16" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B17" s="8">
         <f>'03_Каналы'!B4</f>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B18" s="8">
         <f>'03_Каналы'!B5</f>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B19" s="8">
         <f>'03_Каналы'!B6</f>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" s="8">
         <f>'03_Каналы'!B7</f>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B21" s="8">
         <f>'03_Каналы'!B8</f>
@@ -5537,7 +5537,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" s="8">
         <f>'03_Каналы'!B9</f>
@@ -5572,14 +5572,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="A1" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
       <c r="I1" s="21"/>
@@ -5603,192 +5603,192 @@
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" t="s">
         <v>263</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>264</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" s="3">
+        <v>46298</v>
+      </c>
+      <c r="F4" t="s">
         <v>265</v>
-      </c>
-      <c r="D4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E4" s="3">
-        <v>46144</v>
-      </c>
-      <c r="F4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" t="s">
         <v>268</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>269</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="3">
+        <v>46298</v>
+      </c>
+      <c r="F5" t="s">
         <v>270</v>
-      </c>
-      <c r="D5" t="s">
-        <v>271</v>
-      </c>
-      <c r="E5" s="3">
-        <v>46144</v>
-      </c>
-      <c r="F5" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" t="s">
         <v>273</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>274</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" s="3">
+        <v>46298</v>
+      </c>
+      <c r="F6" t="s">
         <v>275</v>
-      </c>
-      <c r="D6" t="s">
-        <v>276</v>
-      </c>
-      <c r="E6" s="3">
-        <v>46144</v>
-      </c>
-      <c r="F6" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" t="s">
         <v>278</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>279</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" s="3">
+        <v>46298</v>
+      </c>
+      <c r="F7" t="s">
         <v>280</v>
-      </c>
-      <c r="D7" t="s">
-        <v>281</v>
-      </c>
-      <c r="E7" s="3">
-        <v>46144</v>
-      </c>
-      <c r="F7" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C8" t="s">
         <v>283</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>284</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" s="3">
+        <v>46298</v>
+      </c>
+      <c r="F8" t="s">
         <v>285</v>
-      </c>
-      <c r="D8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E8" s="3">
-        <v>46144</v>
-      </c>
-      <c r="F8" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" t="s">
         <v>288</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>289</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" s="3">
+        <v>46298</v>
+      </c>
+      <c r="F9" t="s">
         <v>290</v>
       </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="12" spans="1:26" ht="11" customHeight="1">
+      <c r="A12" s="24" t="s">
         <v>291</v>
       </c>
-      <c r="E9" s="3">
-        <v>46144</v>
-      </c>
-      <c r="F9" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="11" customHeight="1">
-      <c r="A12" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:26" ht="13.9">
       <c r="A13" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="3">
-        <v>46144</v>
+        <v>46298</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="C14" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>360</v>
       </c>
       <c r="E14">
-        <v>18500</v>
+        <v>105975</v>
       </c>
       <c r="F14" t="s">
-        <v>300</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:26">

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_6_объем_рынка_Similarweb_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_6_объем_рынка_Similarweb_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9752330F-07DB-47BD-88F0-B68511B652BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185EEF49-B9D5-48CE-A1CF-001C354B782D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="07_Дашборд" sheetId="8" r:id="rId8"/>
     <sheet name="08_Источники" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1365,7 +1365,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8E23-48CC-8579-DAAE37A913D1}"/>
+              <c16:uniqueId val="{00000000-CDEC-40B9-A230-292BB175EA9D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1413,7 +1413,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8E23-48CC-8579-DAAE37A913D1}"/>
+              <c16:uniqueId val="{00000001-CDEC-40B9-A230-292BB175EA9D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1583,7 +1583,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5C98-4C5C-BD67-3751A6CDCABF}"/>
+              <c16:uniqueId val="{00000000-7D6A-4D42-9047-56D33D6B78E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_6_объем_рынка_Similarweb_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_6_объем_рынка_Similarweb_TableMind.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185EEF49-B9D5-48CE-A1CF-001C354B782D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ECAD7B-EB72-442F-8B99-1FFC380BF38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1365,7 +1365,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CDEC-40B9-A230-292BB175EA9D}"/>
+              <c16:uniqueId val="{00000000-445E-46B7-8511-E1786A35FAC0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1413,7 +1413,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CDEC-40B9-A230-292BB175EA9D}"/>
+              <c16:uniqueId val="{00000001-445E-46B7-8511-E1786A35FAC0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1583,7 +1583,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7D6A-4D42-9047-56D33D6B78E4}"/>
+              <c16:uniqueId val="{00000000-9C1F-4791-BC91-090A90CDAB3F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
